--- a/sync/enriquecidos-template.xlsx
+++ b/sync/enriquecidos-template.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Compatibilidades" sheetId="2" r:id="rId2"/>
     <sheet name="Equivalencias" sheetId="3" r:id="rId3"/>
     <sheet name="Relacionados" sheetId="4" r:id="rId4"/>
+    <sheet name="Especificaciones" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -400,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A45"/>
   <cols>
     <col min="1" max="1" width="90.83203125" customWidth="1"/>
   </cols>
@@ -537,27 +538,62 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>¿DÓNDE GUARDAR?</v>
+        <v xml:space="preserve">  Especificaciones:</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v xml:space="preserve">  - Plantilla (este archivo):  sync/enriquecidos-template.xlsx   (va al repo)</v>
+        <v xml:space="preserve">    - UNA fila por SKU (distinto a las otras hojas).</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">  - Tu copia editada:          sync/enriquecidos.xlsx            (NO va al repo)</v>
+        <v xml:space="preserve">    - Dejá vacías las columnas que no aplican al producto.</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
+        <v xml:space="preserve">    - Columnas: DIENTES, DIAMETRO_CENTRO, PERNOS_CANTIDAD,</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v xml:space="preserve">      DIAMETRO_PERNO, DIAMETRO_PERNO_A_PERNO, TIPO_DE_PASO</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v xml:space="preserve">    - Si todas las columnas están vacías, la sección no aparece en la ficha.</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v xml:space="preserve">    - Pensado para catarinas, discos, prensas, rodamientos, etc.</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>¿DÓNDE GUARDAR?</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v xml:space="preserve">  - Plantilla (este archivo):  sync/enriquecidos-template.xlsx   (va al repo)</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v xml:space="preserve">  - Tu copia editada:          sync/enriquecidos.xlsx            (NO va al repo)</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
         <v xml:space="preserve">  - JSON generado:             data/enriquecidos.json            (va al repo)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A45"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -831,4 +867,162 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G6"/>
+  <cols>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SKU</v>
+      </c>
+      <c r="B1" t="str">
+        <v>DIENTES</v>
+      </c>
+      <c r="C1" t="str">
+        <v>DIAMETRO_CENTRO</v>
+      </c>
+      <c r="D1" t="str">
+        <v>PERNOS_CANTIDAD</v>
+      </c>
+      <c r="E1" t="str">
+        <v>DIAMETRO_PERNO</v>
+      </c>
+      <c r="F1" t="str">
+        <v>DIAMETRO_PERNO_A_PERNO</v>
+      </c>
+      <c r="G1" t="str">
+        <v>TIPO_DE_PASO</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>// EJEMPLOS (borrá los // y poné tu SKU real). Dejá vacías las specs que no aplican.</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>// CATARINA-HONDA-14T</v>
+      </c>
+      <c r="B4" t="str">
+        <v>14T</v>
+      </c>
+      <c r="C4" t="str">
+        <v>20 mm</v>
+      </c>
+      <c r="D4" t="str">
+        <v>5</v>
+      </c>
+      <c r="E4" t="str">
+        <v>8 mm</v>
+      </c>
+      <c r="F4" t="str">
+        <v>42 mm</v>
+      </c>
+      <c r="G4" t="str">
+        <v>428H</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>// CATARINA-BAJAJ-45T</v>
+      </c>
+      <c r="B5" t="str">
+        <v>45T</v>
+      </c>
+      <c r="C5" t="str">
+        <v>58 mm</v>
+      </c>
+      <c r="D5" t="str">
+        <v>5</v>
+      </c>
+      <c r="E5" t="str">
+        <v>8 mm</v>
+      </c>
+      <c r="F5" t="str">
+        <v>58 mm</v>
+      </c>
+      <c r="G5" t="str">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>// DISCO-FRENO-220</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>5</v>
+      </c>
+      <c r="E6" t="str">
+        <v>10.5 mm</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/sync/enriquecidos-template.xlsx
+++ b/sync/enriquecidos-template.xlsx
@@ -8,6 +8,7 @@
     <sheet name="Equivalencias" sheetId="3" r:id="rId3"/>
     <sheet name="Relacionados" sheetId="4" r:id="rId4"/>
     <sheet name="Especificaciones" sheetId="5" r:id="rId5"/>
+    <sheet name="Overrides" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -401,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A55"/>
   <cols>
     <col min="1" max="1" width="90.83203125" customWidth="1"/>
   </cols>
@@ -573,27 +574,72 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>¿DÓNDE GUARDAR?</v>
+        <v xml:space="preserve">  Overrides:</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">  - Plantilla (este archivo):  sync/enriquecidos-template.xlsx   (va al repo)</v>
+        <v xml:space="preserve">    - UNA fila por SKU para sobrescribir el nombre y/o agregar descripción.</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">  - Tu copia editada:          sync/enriquecidos.xlsx            (NO va al repo)</v>
+        <v xml:space="preserve">    - Úsala cuando el nombre del proveedor esté raro, cortado, o quieras</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
+        <v xml:space="preserve">      mejorar la redacción. Gana sobre lo que viene del PDF/Excel/LCR.</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v xml:space="preserve">    - Columnas:</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v xml:space="preserve">      · SKU:          código del producto (debe existir en el catálogo).</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v xml:space="preserve">      · Nombre:       nombre nuevo. Dejá vacío para NO cambiar el nombre.</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v xml:space="preserve">      · Descripcion:  texto largo visible en la ficha. Opcional.</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v xml:space="preserve">    - El nombre nuevo también se usa en búsqueda y compartir por WhatsApp.</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>¿DÓNDE GUARDAR?</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v xml:space="preserve">  - Plantilla (este archivo):  sync/enriquecidos-template.xlsx   (va al repo)</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v xml:space="preserve">  - Tu copia editada:          sync/enriquecidos.xlsx            (NO va al repo)</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
         <v xml:space="preserve">  - JSON generado:             data/enriquecidos.json            (va al repo)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A55"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1025,4 +1071,108 @@
     <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="50.83203125" customWidth="1"/>
+    <col min="3" max="3" width="80.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SKU</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Nombre</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Descripcion</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1002389</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Cigüeñal GY6 150cc Scooter</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Cigüeñal balanceado, compatible con scooters GY6 150cc. Incluye biela y rodamientos.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>// EJEMPLOS (borrá los // y poné tu SKU real)</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>// MI-SKU-123</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Nombre nuevo más claro</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>// MI-SKU-456</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v>Descripción extendida que aparece en la ficha del producto.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>// Si solo querés cambiar el NOMBRE, dejá Descripcion vacía.</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>// Si solo querés agregar DESCRIPCIÓN sin cambiar el nombre, dejá Nombre vacío.</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+  </ignoredErrors>
+</worksheet>
 </file>